--- a/pauta_focalizada_pcsp.xlsx
+++ b/pauta_focalizada_pcsp.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_eventos_pcsp" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_metodologia'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_metodologia'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_ranking_cuadrantes'!$A$1:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_puntos_focalizados'!$A$1:$U$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_celdas_criticas'!$A$1:$F$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_puntos_focalizados'!$A$1:$U$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_celdas_criticas'!$A$1:$F$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_eventos_pcsp'!$A$1:$F$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,10 +439,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -519,7 +519,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tamaño_grilla_general_m</t>
+          <t>grilla_general_m</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -529,11 +529,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tamaño_grilla_delta_m</t>
+          <t>grilla_delta_m</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -575,27 +575,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>distancia_fusion_intersecciones_m</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
           <t>fecha_generacion</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-12 01:54:10</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-12 13:04:39</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1484,7 +1474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1505,9 +1495,9 @@
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1608,12 +1598,12 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>tamano_grilla_m</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>url_google_maps</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>url_survey123</t>
         </is>
       </c>
     </row>
@@ -1643,24 +1633,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chacabuco &amp; Monumento</t>
+          <t>Los Pajaritos &amp; Maipu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1669,16 +1659,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-33.5090537</v>
+        <v>-33.5069714</v>
       </c>
       <c r="O2" t="n">
-        <v>-70.758838</v>
+        <v>-70.75733030000001</v>
       </c>
       <c r="P2" t="n">
-        <v>48.9</v>
+        <v>8.4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1687,20 +1677,22 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Chacabuco &amp; Monumento</t>
+          <t>Los Pajaritos &amp; Maipu</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>218C_G0041</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5090537,-70.7588380&amp;travelmode=walking</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
+          <t>218C_D00267</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5069714,-70.7573303&amp;travelmode=walking</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1728,24 +1720,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Los Pajaritos &amp; Maipu</t>
+          <t>Chacabuco &amp; Monumento</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1754,16 +1746,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>-33.5069714</v>
+        <v>-33.5090537</v>
       </c>
       <c r="O3" t="n">
-        <v>-70.75733030000001</v>
+        <v>-70.758838</v>
       </c>
       <c r="P3" t="n">
-        <v>8.4</v>
+        <v>48.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1772,20 +1764,22 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Los Pajaritos &amp; Maipu</t>
+          <t>Chacabuco &amp; Monumento</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>218C_G0060</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5069714,-70.7573303&amp;travelmode=walking</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
+          <t>218C_D00191</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5090537,-70.7588380&amp;travelmode=walking</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1813,42 +1807,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Amado Nervo &amp; Bramante</t>
+          <t>Iniciacion &amp; Los Capuchinos</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-33.4736521</v>
+        <v>-33.4730838</v>
       </c>
       <c r="O4" t="n">
-        <v>-70.72865760000001</v>
+        <v>-70.73251740000001</v>
       </c>
       <c r="P4" t="n">
-        <v>38.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1857,20 +1851,22 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Amado Nervo &amp; Bramante</t>
+          <t>Iniciacion &amp; Los Capuchinos</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>215C_G0019</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4736521,-70.7286576&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+          <t>G01547</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>400</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4730838,-70.7325174&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1898,7 +1894,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andalucia &amp; Hijos De Maria</t>
+          <t>Dublin &amp; Las Parcelas</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1912,10 +1908,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1927,13 +1923,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-33.473259</v>
+        <v>-33.4758398</v>
       </c>
       <c r="O5" t="n">
-        <v>-70.732225</v>
+        <v>-70.7337339</v>
       </c>
       <c r="P5" t="n">
-        <v>38.6</v>
+        <v>15.6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1942,20 +1938,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Andalucia &amp; Hijos De Maria</t>
+          <t>Dublin &amp; Las Parcelas</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>215C_G0014</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4732590,-70.7322250&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
+          <t>G01546</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>400</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4758398,-70.7337339&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1983,27 +1981,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Las Parcelas &amp; Manchester</t>
+          <t>El Duraznal &amp; Las Torres</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2012,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-33.4763026</v>
+        <v>-33.4781355</v>
       </c>
       <c r="O6" t="n">
-        <v>-70.7345766</v>
+        <v>-70.7315126</v>
       </c>
       <c r="P6" t="n">
-        <v>87.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -2027,20 +2025,22 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Las Parcelas &amp; Manchester</t>
+          <t>El Duraznal &amp; Las Torres</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>215C_G0013</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4763026,-70.7345766&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
+          <t>G01545</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>400</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4781355,-70.7315126&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2068,17 +2068,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botswana &amp; Costa De Marfil</t>
+          <t>Doctor Livingstone &amp; Nigeria</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-33.4778055</v>
+        <v>-33.4800894</v>
       </c>
       <c r="O7" t="n">
-        <v>-70.73698539999999</v>
+        <v>-70.734459</v>
       </c>
       <c r="P7" t="n">
-        <v>75.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -2112,20 +2112,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Botswana &amp; Costa De Marfil</t>
+          <t>Doctor Livingstone &amp; Nigeria</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>215C_G0008</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4778055,-70.7369854&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
+          <t>G01545</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>400</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4800894,-70.7344590&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2153,7 +2155,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enrique Stanley &amp; Tierra Del Fuego</t>
+          <t>Dakar &amp; Doctor Livingstone</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2163,11 +2165,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado + Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2176,19 +2178,19 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-33.4790873</v>
+        <v>-33.4780465</v>
       </c>
       <c r="O8" t="n">
-        <v>-70.7321713</v>
+        <v>-70.7360923</v>
       </c>
       <c r="P8" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -2197,20 +2199,22 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Enrique Stanley &amp; Tierra Del Fuego</t>
+          <t>Dakar &amp; Doctor Livingstone</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>215C_G0012</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4790873,-70.7321713&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
+          <t>G01512</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>400</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4780465,-70.7360923&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2220,7 +2224,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_216B_008</t>
+          <t>PF_PCSP_20260406_20260503_215C_008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2230,15 +2234,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>216B</t>
+          <t>215C</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Las Achileas &amp; Los Copihues</t>
+          <t>Amado Nervo &amp; Bramante</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2252,7 +2256,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2261,19 +2265,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-33.4868202</v>
+        <v>-33.474024</v>
       </c>
       <c r="O9" t="n">
-        <v>-70.77128209999999</v>
+        <v>-70.7285696</v>
       </c>
       <c r="P9" t="n">
-        <v>108.7</v>
+        <v>35.8</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -2282,20 +2286,22 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Las Achileas &amp; Los Copihues</t>
+          <t>Amado Nervo &amp; Bramante</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>216B_G0006</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4868202,-70.7712821&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+          <t>G01580</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>400</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4740240,-70.7285696&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2319,46 +2325,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10 De Julio &amp; 9 De Julio</t>
+          <t>Teatro Opera &amp; Teatro Recoleta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-33.4893832</v>
+        <v>-33.4907514</v>
       </c>
       <c r="O10" t="n">
-        <v>-70.7683007</v>
+        <v>-70.7651177</v>
       </c>
       <c r="P10" t="n">
-        <v>26.3</v>
+        <v>6.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -2367,20 +2373,22 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10 De Julio &amp; 9 De Julio</t>
+          <t>Teatro Opera &amp; Teatro Recoleta</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>216B_G0008</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4893832,-70.7683007&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
+          <t>G01311</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>400</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4907514,-70.7651177&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2404,28 +2412,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Teatro Monumental &amp; Teatro Opera</t>
+          <t>Claudio Arrau &amp; Clavicordio</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -2434,16 +2442,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>-33.4909391</v>
+        <v>-33.4906129</v>
       </c>
       <c r="O11" t="n">
-        <v>-70.76514760000001</v>
+        <v>-70.763896</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>25.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2452,20 +2460,22 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Teatro Monumental &amp; Teatro Opera</t>
+          <t>Claudio Arrau &amp; Clavicordio</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>216B_G0014</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4909391,-70.7651476&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
+          <t>G01311</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>400</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4906129,-70.7638960&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2489,21 +2499,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arquitecto Eduardo Jedlicki &amp; Claudio Arrau</t>
+          <t>10 De Julio &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -2516,19 +2526,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-33.4901655</v>
+        <v>-33.4896701</v>
       </c>
       <c r="O12" t="n">
-        <v>-70.7643063</v>
+        <v>-70.7688747</v>
       </c>
       <c r="P12" t="n">
-        <v>51.6</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2537,20 +2547,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Arquitecto Eduardo Jedlicki &amp; Claudio Arrau</t>
+          <t>10 De Julio &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>216B_G0014</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4901655,-70.7643063&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr"/>
+          <t>G01278</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>400</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4896701,-70.7688747&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2574,21 +2586,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>La Citara &amp; La Sinfonia</t>
+          <t>Batalla De Rancagua &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2601,19 +2613,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-33.4903009</v>
+        <v>-33.4878412</v>
       </c>
       <c r="O13" t="n">
-        <v>-70.7571552</v>
+        <v>-70.7704572</v>
       </c>
       <c r="P13" t="n">
-        <v>86.59999999999999</v>
+        <v>30.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2622,20 +2634,22 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>La Citara &amp; La Sinfonia</t>
+          <t>Batalla De Rancagua &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>216B_G0021</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4903009,-70.7571552&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+          <t>G01246</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>400</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4878412,-70.7704572&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2659,21 +2673,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Rosal &amp; Las Araucarias</t>
+          <t>La Sinfonia &amp; Volcan Maipo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -2683,22 +2697,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>-33.4803684</v>
+        <v>-33.4897414</v>
       </c>
       <c r="O14" t="n">
-        <v>-70.7601743</v>
+        <v>-70.7575111</v>
       </c>
       <c r="P14" t="n">
-        <v>26.8</v>
+        <v>16.3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2707,20 +2721,22 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>El Rosal &amp; Las Araucarias</t>
+          <t>La Sinfonia &amp; Volcan Maipo</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>216B_G0024</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4803684,-70.7601743&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
+          <t>G01344</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>400</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4897414,-70.7575111&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2730,7 +2746,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_220A_014</t>
+          <t>PF_PCSP_20260406_20260503_216B_014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2740,50 +2756,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>220A</t>
+          <t>216B</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cuatro Poniente &amp; Libertador De Chile</t>
+          <t>El Rosal &amp; Las Araucarias</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Robos violentos + Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-33.503081</v>
+        <v>-33.4803684</v>
       </c>
       <c r="O15" t="n">
-        <v>-70.791173</v>
+        <v>-70.7601743</v>
       </c>
       <c r="P15" t="n">
-        <v>83.3</v>
+        <v>26.8</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2792,20 +2808,22 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Cuatro Poniente &amp; Libertador De Chile</t>
+          <t>El Rosal &amp; Las Araucarias</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>220A_G0009 | 220A_G0013</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5030810,-70.7911730&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
+          <t>G01347</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>400</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4803684,-70.7601743&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2829,11 +2847,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Del Cacique &amp; Pangal</t>
+          <t>Libertador Bernardo O'higgins &amp; Paso De Los Patos</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2843,32 +2861,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos + Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-33.5076702</v>
+        <v>-33.5035963</v>
       </c>
       <c r="O16" t="n">
-        <v>-70.78618040000001</v>
+        <v>-70.7907591</v>
       </c>
       <c r="P16" t="n">
-        <v>337.6</v>
+        <v>45.3</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2877,20 +2895,22 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Del Cacique &amp; Pangal</t>
+          <t>Calera &amp; Cuatro Poniente | Libertador Bernardo O'higgins &amp; Paso De Los Patos</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>220A_G0016</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5076702,-70.7861804&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>G01076 | G01109</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>400</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5035963,-70.7907591&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2900,7 +2920,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_220B_016</t>
+          <t>PF_PCSP_20260406_20260503_220A_016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2910,15 +2930,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>220B</t>
+          <t>220A</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Agua Santa &amp; Chinquihue</t>
+          <t>Dawson &amp; Futaleufu</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2928,7 +2948,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado + Violencia intrafamiliar</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2938,22 +2958,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-33.5147972</v>
+        <v>-33.5113905</v>
       </c>
       <c r="O17" t="n">
-        <v>-70.7893936</v>
+        <v>-70.78606430000001</v>
       </c>
       <c r="P17" t="n">
-        <v>123.7</v>
+        <v>53.8</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2962,20 +2982,22 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Agua Santa &amp; Chinquihue</t>
+          <t>Dawson &amp; Futaleufu</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>220B_G0012</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5147972,-70.7893936&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
+          <t>G01140</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>400</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5113905,-70.7860643&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2999,25 +3021,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Licurgo &amp; San Jose</t>
+          <t>El Huaso &amp; Euridice</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -3026,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-33.5174177</v>
+        <v>-33.5145065</v>
       </c>
       <c r="O18" t="n">
-        <v>-70.79389159999999</v>
+        <v>-70.7890127</v>
       </c>
       <c r="P18" t="n">
-        <v>102.1</v>
+        <v>77.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3047,20 +3069,22 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Licurgo &amp; San Jose</t>
+          <t>El Huaso &amp; Euridice</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>220B_G0007</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5174177,-70.7938916&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
+          <t>G01106</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>400</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5145065,-70.7890127&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3084,21 +3108,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; Las Tinajas</t>
+          <t>Alceo &amp; Esquilo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -3111,19 +3135,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>-33.5163693</v>
+        <v>-33.5185121</v>
       </c>
       <c r="O19" t="n">
-        <v>-70.7968735</v>
+        <v>-70.79471940000001</v>
       </c>
       <c r="P19" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3132,20 +3156,22 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; Las Tinajas</t>
+          <t>Alceo &amp; Esquilo</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>220B_G0004</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5163693,-70.7968735&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
+          <t>G01072</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>400</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185121,-70.7947194&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3169,7 +3195,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3183,17 +3209,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Robos violentos + Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -3202,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-33.5205186</v>
+        <v>-33.5205503</v>
       </c>
       <c r="O20" t="n">
-        <v>-70.7960458</v>
+        <v>-70.79690189999999</v>
       </c>
       <c r="P20" t="n">
-        <v>74.7</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3222,15 +3248,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>220B_G0002</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5205186,-70.7960458&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
+          <t>G01038</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>400</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5205503,-70.7969019&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3254,7 +3282,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3263,22 +3291,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robo en lugar habitado + Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -3287,13 +3315,13 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>-33.522186</v>
+        <v>-33.522027</v>
       </c>
       <c r="O21" t="n">
-        <v>-70.7972827</v>
+        <v>-70.7969271</v>
       </c>
       <c r="P21" t="n">
-        <v>49.6</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3307,15 +3335,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>220B_G0002</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5221860,-70.7972827&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
+          <t>G01038</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>400</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5220270,-70.7969271&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3339,46 +3369,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Discovery &amp; Los Astronomos</t>
+          <t>El Conquistador &amp; Las Tinajas</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-33.5246153</v>
+        <v>-33.5163693</v>
       </c>
       <c r="O22" t="n">
-        <v>-70.79846689999999</v>
+        <v>-70.7968735</v>
       </c>
       <c r="P22" t="n">
-        <v>67.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3387,20 +3417,22 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Discovery &amp; Los Astronomos</t>
+          <t>El Conquistador &amp; Las Tinajas</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>220B_G0001</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5246153,-70.7984669&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
+          <t>G01040</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>400</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5163693,-70.7968735&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3410,7 +3442,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_221A_022</t>
+          <t>PF_PCSP_20260406_20260503_220B_022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3420,35 +3452,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>221A</t>
+          <t>220B</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bosquealto &amp; Catemu</t>
+          <t>Andromeda &amp; El Conquistador</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3457,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-33.5330551</v>
+        <v>-33.5146254</v>
       </c>
       <c r="O23" t="n">
-        <v>-70.79715330000001</v>
+        <v>-70.79698380000001</v>
       </c>
       <c r="P23" t="n">
-        <v>62.1</v>
+        <v>21.4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3472,20 +3504,22 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Bosquealto &amp; Catemu</t>
+          <t>Andromeda &amp; El Conquistador</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>221A_G0017</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5330551,-70.7971533&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
+          <t>G01040</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>400</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5146254,-70.7969838&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3509,46 +3543,46 @@
         </is>
       </c>
       <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bosquealto &amp; Catemu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Cam Del Leñador &amp; Chillan Viejo</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-33.5340559</v>
+        <v>-33.53279</v>
       </c>
       <c r="O24" t="n">
-        <v>-70.8000578</v>
+        <v>-70.79795129999999</v>
       </c>
       <c r="P24" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3557,20 +3591,22 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Cam Del Leñador &amp; Chillan Viejo</t>
+          <t>Bosquealto &amp; Catemu</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>221A_G0017</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5340559,-70.8000578&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
+          <t>G01035</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>400</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5327900,-70.7979513&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3594,11 +3630,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
+          <t>Cam Del Leñador &amp; Litueche</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3627,13 +3663,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-33.5286591</v>
+        <v>-33.5340813</v>
       </c>
       <c r="O25" t="n">
-        <v>-70.7973439</v>
+        <v>-70.79976929999999</v>
       </c>
       <c r="P25" t="n">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3642,20 +3678,22 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
+          <t>Cam Del Leñador &amp; Litueche</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>221A_G0018</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5286591,-70.7973439&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
+          <t>G01035</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>400</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5340813,-70.7997693&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3679,31 +3717,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arq. Pedro Barros P. &amp; Cam El Bosque</t>
+          <t>Alfredo Silva Carvallo &amp; Cuatro Poniente</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3712,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-33.5463418</v>
+        <v>-33.5319846</v>
       </c>
       <c r="O26" t="n">
-        <v>-70.7913424</v>
+        <v>-70.79345929999999</v>
       </c>
       <c r="P26" t="n">
-        <v>69.09999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3727,20 +3765,22 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Arq. Pedro Barros P. &amp; Cam El Bosque</t>
+          <t>Alfredo Silva Carvallo &amp; Cuatro Poniente</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>221A_G0030</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5463418,-70.7913424&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr"/>
+          <t>G01068</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>400</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5319846,-70.7934593&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3750,60 +3790,60 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_217A_026</t>
+          <t>PF_PCSP_20260406_20260503_221A_026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>217A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anunciacion &amp; Judith</t>
+          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-33.4954801</v>
+        <v>-33.5286591</v>
       </c>
       <c r="O27" t="n">
-        <v>-70.75527080000001</v>
+        <v>-70.7973439</v>
       </c>
       <c r="P27" t="n">
-        <v>49.4</v>
+        <v>42.5</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3812,20 +3852,22 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Anunciacion &amp; Judith</t>
+          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>217A_G0007</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4954801,-70.7552708&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
+          <t>G01036</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>400</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5286591,-70.7973439&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3835,60 +3877,60 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_217A_027</t>
+          <t>PF_PCSP_20260406_20260503_221A_027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>217A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cecilia &amp; Epu</t>
+          <t>Faro De Alejandria &amp; Rosita Renard</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-33.4947473</v>
+        <v>-33.5256375</v>
       </c>
       <c r="O28" t="n">
-        <v>-70.7531499</v>
+        <v>-70.7983357</v>
       </c>
       <c r="P28" t="n">
-        <v>36.9</v>
+        <v>180.9</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -3897,20 +3939,22 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Cecilia &amp; Epu</t>
+          <t>Faro De Alejandria &amp; Rosita Renard</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>217A_G0008</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4947473,-70.7531499&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr"/>
+          <t>G01037</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>400</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5256375,-70.7983357&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3920,25 +3964,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_217A_028</t>
+          <t>PF_PCSP_20260406_20260503_221A_028</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>217A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carlos Cruz &amp; Jose Miguel Ramirez</t>
+          <t>El Sauco &amp; Portal Del Bosque</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3967,13 +4011,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-33.4988379</v>
+        <v>-33.5458374</v>
       </c>
       <c r="O29" t="n">
-        <v>-70.7547807</v>
+        <v>-70.7901864</v>
       </c>
       <c r="P29" t="n">
-        <v>39</v>
+        <v>78.5</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -3982,20 +4026,22 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Carlos Cruz &amp; Jose Miguel Ramirez</t>
+          <t>El Sauco &amp; Portal Del Bosque</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>217A_G0006</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4988379,-70.7547807&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr"/>
+          <t>G01097</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>400</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5458374,-70.7901864&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4019,31 +4065,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grumete Bustos &amp; Presidente Kennedy</t>
+          <t>Anunciacion &amp; Judith</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4052,13 +4098,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-33.5034084</v>
+        <v>-33.4955146</v>
       </c>
       <c r="O30" t="n">
-        <v>-70.7490274</v>
+        <v>-70.7550313</v>
       </c>
       <c r="P30" t="n">
-        <v>55.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4067,20 +4113,22 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Grumete Bustos &amp; Presidente Kennedy</t>
+          <t>Anunciacion &amp; Judith</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>217A_G0012</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5034084,-70.7490274&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
+          <t>G01375</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>400</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4955146,-70.7550313&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4104,11 +4152,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Presidente Kennedy &amp; Uno Sur</t>
+          <t>Cecilia &amp; Meli</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4137,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-33.506299</v>
+        <v>-33.4950829</v>
       </c>
       <c r="O31" t="n">
-        <v>-70.74939689999999</v>
+        <v>-70.75292399999999</v>
       </c>
       <c r="P31" t="n">
-        <v>16.8</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4152,20 +4200,22 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Presidente Kennedy &amp; Uno Sur</t>
+          <t>Cecilia &amp; Meli</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>217A_G0012</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5062990,-70.7493969&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>G01376</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>400</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4950829,-70.7529240&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4189,28 +4239,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Americo Vespucio &amp; Antares</t>
+          <t>Central Gonzalo Perez Llona &amp; Primera Transversal</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -4219,16 +4269,16 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-33.4984568</v>
+        <v>-33.5002405</v>
       </c>
       <c r="O32" t="n">
-        <v>-70.74445609999999</v>
+        <v>-70.75199139999999</v>
       </c>
       <c r="P32" t="n">
-        <v>17.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4237,20 +4287,22 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Americo Vespucio &amp; Antares</t>
+          <t>Central Gonzalo Perez Llona &amp; Primera Transversal</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>217A_G0021</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4984568,-70.7444561&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>G01407</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>400</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5002405,-70.7519914&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4260,7 +4312,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_218B_032</t>
+          <t>PF_PCSP_20260406_20260503_217A_032</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4270,35 +4322,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>218B</t>
+          <t>217A</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Campanario &amp; El Principe</t>
+          <t>Covadonga &amp; El Sol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4307,13 +4359,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-33.519661</v>
+        <v>-33.5034736</v>
       </c>
       <c r="O33" t="n">
-        <v>-70.7714407</v>
+        <v>-70.7498313</v>
       </c>
       <c r="P33" t="n">
-        <v>19.2</v>
+        <v>30.6</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4322,20 +4374,22 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Campanario &amp; El Principe</t>
+          <t>Covadonga &amp; El Sol</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>218B_G0007</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5196610,-70.7714407&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>G01406</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>400</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5034736,-70.7498313&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4345,7 +4399,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_218B_033</t>
+          <t>PF_PCSP_20260406_20260503_217A_033</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4355,50 +4409,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>218B</t>
+          <t>217A</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Del Rey &amp; Los Escritores</t>
+          <t>Presidente Kennedy &amp; Uno Sur</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-33.5185017</v>
+        <v>-33.506299</v>
       </c>
       <c r="O34" t="n">
-        <v>-70.770884</v>
+        <v>-70.74939689999999</v>
       </c>
       <c r="P34" t="n">
-        <v>10.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4407,20 +4461,22 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Del Rey &amp; Los Escritores</t>
+          <t>Presidente Kennedy &amp; Uno Sur</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>218B_G0007</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185017,-70.7708840&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr"/>
+          <t>G01406</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>400</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5062990,-70.7493969&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4430,7 +4486,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_218B_034</t>
+          <t>PF_PCSP_20260406_20260503_217A_034</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4440,25 +4496,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>218B</t>
+          <t>217A</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Olimpo &amp; Las Tinajas</t>
+          <t>5 De Abril &amp; Segunda Transversal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -4471,19 +4527,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>-33.5152946</v>
+        <v>-33.5103631</v>
       </c>
       <c r="O35" t="n">
-        <v>-70.7754329</v>
+        <v>-70.74719260000001</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4492,20 +4548,22 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>El Olimpo &amp; Las Tinajas</t>
+          <t>5 De Abril &amp; Segunda Transversal</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>218B_G0003</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5152946,-70.7754329&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr"/>
+          <t>G01438</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>400</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5103631,-70.7471926&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4529,11 +4587,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alemania &amp; Jose Manuel Borgoño</t>
+          <t>Campanario &amp; El Principe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4543,11 +4601,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robo en lugar habitado + Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4556,19 +4614,19 @@
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-33.5117929</v>
+        <v>-33.519661</v>
       </c>
       <c r="O36" t="n">
-        <v>-70.77179270000001</v>
+        <v>-70.7714407</v>
       </c>
       <c r="P36" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -4577,20 +4635,22 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Alemania &amp; Jose Manuel Borgoño</t>
+          <t>Campanario &amp; Del Rey | Campanario &amp; El Principe</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>218B_G0009</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5117929,-70.7717927&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr"/>
+          <t>G01237 | G01270</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>400</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5196610,-70.7714407&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4614,46 +4674,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cardenal Samore &amp; Del Pontifice</t>
+          <t>Del Rey &amp; Los Escritores</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-33.5130988</v>
+        <v>-33.5185017</v>
       </c>
       <c r="O37" t="n">
-        <v>-70.76707330000001</v>
+        <v>-70.770884</v>
       </c>
       <c r="P37" t="n">
-        <v>96.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -4662,20 +4722,22 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Cardenal Samore &amp; Del Pontifice</t>
+          <t>Del Rey &amp; Los Escritores</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>218B_G0015</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5130988,-70.7670733&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
+          <t>G01237</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>400</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185017,-70.7708840&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4699,25 +4761,25 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
+          <t>Del Pontifice &amp; Republica</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4726,19 +4788,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-33.5208043</v>
+        <v>-33.5129099</v>
       </c>
       <c r="O38" t="n">
-        <v>-70.7589186</v>
+        <v>-70.7670775</v>
       </c>
       <c r="P38" t="n">
-        <v>15.3</v>
+        <v>81.7</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -4747,20 +4809,22 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
+          <t>Del Pontifice &amp; Republica</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>218B_G0024</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5208043,-70.7589186&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
+          <t>G01272</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>400</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5129099,-70.7670775&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4770,7 +4834,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_219_038</t>
+          <t>PF_PCSP_20260406_20260503_218B_038</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4780,50 +4844,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218B</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ciclope &amp; El Olimpo</t>
+          <t>Alemania &amp; Jose Manuel Borgoño</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-33.5032627</v>
+        <v>-33.5117929</v>
       </c>
       <c r="O39" t="n">
-        <v>-70.7756758</v>
+        <v>-70.77179270000001</v>
       </c>
       <c r="P39" t="n">
-        <v>118.1</v>
+        <v>18.2</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -4832,20 +4896,22 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Ciclope &amp; El Olimpo</t>
+          <t>Alemania &amp; Jose Manuel Borgoño</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>219_G0025</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5032627,-70.7756758&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr"/>
+          <t>G01239</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>400</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5117929,-70.7717927&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4855,7 +4921,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_219_039</t>
+          <t>PF_PCSP_20260406_20260503_218B_039</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4865,29 +4931,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218B</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colibri &amp; Los Faisanes</t>
+          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4896,19 +4962,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>-33.5178303</v>
+        <v>-33.520565</v>
       </c>
       <c r="O40" t="n">
-        <v>-70.77691249999999</v>
+        <v>-70.7590924</v>
       </c>
       <c r="P40" t="n">
-        <v>67.3</v>
+        <v>15.8</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -4917,20 +4983,22 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Colibri &amp; Los Faisanes</t>
+          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>219_G0020</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5178303,-70.7769125&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
+          <t>G01336</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>400</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5205650,-70.7590924&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4954,46 +5022,46 @@
         </is>
       </c>
       <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Amaltea &amp; El Olimpo</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
         <v>3</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Colibri &amp; Filidor</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-33.5193271</v>
+        <v>-33.5024761</v>
       </c>
       <c r="O41" t="n">
-        <v>-70.77615299999999</v>
+        <v>-70.7755947</v>
       </c>
       <c r="P41" t="n">
-        <v>48.7</v>
+        <v>33.9</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5002,20 +5070,22 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Colibri &amp; Filidor</t>
+          <t>Amaltea &amp; El Olimpo</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>219_G0020</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5193271,-70.7761530&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr"/>
+          <t>G01209</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>400</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5024761,-70.7755947&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5039,46 +5109,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monjas Francesas &amp; Sur</t>
+          <t>Chinquihue &amp; El Cequion</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-33.5219373</v>
+        <v>-33.5141403</v>
       </c>
       <c r="O42" t="n">
-        <v>-70.7851737</v>
+        <v>-70.7851647</v>
       </c>
       <c r="P42" t="n">
-        <v>89.7</v>
+        <v>68</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5087,20 +5157,22 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Monjas Francesas &amp; Sur</t>
+          <t>Chinquihue &amp; El Cequion</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>219_G0002</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5219373,-70.7851737&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr"/>
+          <t>G01139</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>400</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5141403,-70.7851647&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5110,7 +5182,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_222A_042</t>
+          <t>PF_PCSP_20260406_20260503_219_042</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5120,35 +5192,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Actor Fernando Gallardo &amp; Alaska</t>
+          <t>Disprosio &amp; Las Olimpiadas</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5157,13 +5229,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-33.4887324</v>
+        <v>-33.5218854</v>
       </c>
       <c r="O43" t="n">
-        <v>-70.737489</v>
+        <v>-70.78387189999999</v>
       </c>
       <c r="P43" t="n">
-        <v>184.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -5172,20 +5244,22 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Actor Fernando Gallardo &amp; Alaska</t>
+          <t>Disprosio &amp; Las Olimpiadas</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>222A_G0016</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4887324,-70.7374890&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>G01137</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>400</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5218854,-70.7838719&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5195,7 +5269,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_222A_043</t>
+          <t>PF_PCSP_20260406_20260503_219_043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5205,32 +5279,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Filidor &amp; Los Coros</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Leningrado &amp; Moscu</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5242,13 +5316,13 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-33.4883169</v>
+        <v>-33.5185804</v>
       </c>
       <c r="O44" t="n">
-        <v>-70.734066</v>
+        <v>-70.7759921</v>
       </c>
       <c r="P44" t="n">
-        <v>73.5</v>
+        <v>43.7</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -5257,20 +5331,22 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Leningrado &amp; Moscu</t>
+          <t>Filidor &amp; Los Coros</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>222A_G0020</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4883169,-70.7340660&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr"/>
+          <t>G01204</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>400</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185804,-70.7759921&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5294,31 +5370,31 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Isla De Cuba &amp; Isla Guadalupe</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5327,13 +5403,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-33.4915029</v>
+        <v>-33.4874962</v>
       </c>
       <c r="O45" t="n">
-        <v>-70.7407054</v>
+        <v>-70.737493</v>
       </c>
       <c r="P45" t="n">
-        <v>134.2</v>
+        <v>47.3</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -5342,20 +5418,22 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Isla De Cuba &amp; Isla Guadalupe</t>
+          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>222A_G0009</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4915029,-70.7407054&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
+          <t>G01510</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>400</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4874962,-70.7374930&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5379,31 +5457,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>El Caiquen &amp; Las Alondras</t>
+          <t>Hernando Bravo &amp; Juan Bohon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5412,13 +5490,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-33.4930848</v>
+        <v>-33.4891265</v>
       </c>
       <c r="O46" t="n">
-        <v>-70.7397636</v>
+        <v>-70.7348198</v>
       </c>
       <c r="P46" t="n">
-        <v>77.5</v>
+        <v>53.2</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -5427,20 +5505,22 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>El Caiquen &amp; Las Alondras</t>
+          <t>Hernando Bravo &amp; Juan Bohon</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>222A_G0008</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4930848,-70.7397636&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>G01542</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>400</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4891265,-70.7348198&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5464,46 +5544,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Puerto Cardenas &amp; Puerto Viejo</t>
+          <t>Carmela Larrain &amp; Dolores Bernales</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-33.4938426</v>
+        <v>-33.4898862</v>
       </c>
       <c r="O47" t="n">
-        <v>-70.745209</v>
+        <v>-70.7398524</v>
       </c>
       <c r="P47" t="n">
-        <v>35.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -5512,20 +5592,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Puerto Cardenas &amp; Puerto Viejo</t>
+          <t>Carmela Larrain &amp; Dolores Bernales</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>222A_G0003</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4938426,-70.7452090&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr"/>
+          <t>G01476</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>400</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4898862,-70.7398524&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5549,46 +5631,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anacondas &amp; Apaches</t>
+          <t>El Pesebre &amp; La Adoracion</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-33.4959302</v>
+        <v>-33.4939805</v>
       </c>
       <c r="O48" t="n">
-        <v>-70.7346242</v>
+        <v>-70.7400719</v>
       </c>
       <c r="P48" t="n">
-        <v>163.3</v>
+        <v>49.7</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5597,20 +5679,22 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Anacondas &amp; Apaches</t>
+          <t>El Pesebre &amp; La Adoracion</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>222A_G0013</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4959302,-70.7346242&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr"/>
+          <t>G01475</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>400</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4939805,-70.7400719&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5620,7 +5704,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_223B_048</t>
+          <t>PF_PCSP_20260406_20260503_222A_048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5630,15 +5714,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Constitucion &amp; Pelarco</t>
+          <t>Lumen &amp; Tres Norte</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5667,13 +5751,13 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-33.5461868</v>
+        <v>-33.4959182</v>
       </c>
       <c r="O49" t="n">
-        <v>-70.7621163</v>
+        <v>-70.7365563</v>
       </c>
       <c r="P49" t="n">
-        <v>83.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5682,20 +5766,22 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Constitucion &amp; Pelarco</t>
+          <t>Lumen &amp; Tres Norte</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>223B_G0041</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5461868,-70.7621163&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t>G01507</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>400</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4959182,-70.7365563&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5705,7 +5791,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_223B_049</t>
+          <t>PF_PCSP_20260406_20260503_222A_049</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5715,50 +5801,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caronte &amp; Constantinopla Poniente</t>
+          <t>Alonso De Ercilla &amp; Jose Santos Gonzalez</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-33.5498416</v>
+        <v>-33.4942642</v>
       </c>
       <c r="O50" t="n">
-        <v>-70.7721276</v>
+        <v>-70.7451442</v>
       </c>
       <c r="P50" t="n">
-        <v>90.90000000000001</v>
+        <v>30.8</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5767,20 +5853,22 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Caronte &amp; Constantinopla Poniente</t>
+          <t>Alonso De Ercilla &amp; Jose Santos Gonzalez</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>223B_G0017</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5498416,-70.7721276&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr"/>
+          <t>G01442</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>400</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4942642,-70.7451442&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5804,46 +5892,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cabo De Hoom &amp; Esdras</t>
+          <t>Empedrado &amp; Israel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-33.5468073</v>
+        <v>-33.5458136</v>
       </c>
       <c r="O51" t="n">
-        <v>-70.77925140000001</v>
+        <v>-70.76161089999999</v>
       </c>
       <c r="P51" t="n">
-        <v>146.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5852,20 +5940,22 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Cabo De Hoom &amp; Esdras</t>
+          <t>Empedrado &amp; Israel</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>223B_G0007</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5468073,-70.7792514&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr"/>
+          <t>G01329</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>400</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5458136,-70.7616109&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5889,31 +5979,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Adriana Perez Llona &amp; Diputado Angel Fantuzzi Hernandez</t>
+          <t>Caronte &amp; El Libano Poniente</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -5922,13 +6012,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-33.5447336</v>
+        <v>-33.54948</v>
       </c>
       <c r="O52" t="n">
-        <v>-70.7791479</v>
+        <v>-70.7728819</v>
       </c>
       <c r="P52" t="n">
-        <v>34.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5937,20 +6027,22 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Adriana Perez Llona &amp; Diputado Angel Fantuzzi Hernandez</t>
+          <t>Caronte &amp; El Libano Poniente</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>223B_G0013</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5447336,-70.7791479&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr"/>
+          <t>G01228</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>400</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5494800,-70.7728819&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5974,71 +6066,247 @@
         </is>
       </c>
       <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Diputado Angel Fantuzzi Hernandez &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-33.5450065</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-70.7793266</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>mismo_cuadrante</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Diputado Angel Fantuzzi Hernandez &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>G01197</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>400</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5450065,-70.7793266&amp;travelmode=driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503_223B_053</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Esdras &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-33.5461565</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-70.78067249999999</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>mismo_cuadrante</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Esdras &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>G01163</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>400</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5461565,-70.7806725&amp;travelmode=driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503_223B_054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
         <v>5</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Cam A Melipilla &amp; Etiopia</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-33.5417962</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-70.77763179999999</v>
-      </c>
-      <c r="P53" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="Q53" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Heliopolis &amp; Sahara</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-33.542362</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-70.7769976</v>
+      </c>
+      <c r="P55" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>mismo_cuadrante</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Cam A Melipilla &amp; Etiopia</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>223B_G0013</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5417962,-70.7776318&amp;travelmode=driving</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Heliopolis &amp; Sahara</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>G01197</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>400</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5423620,-70.7769976&amp;travelmode=driving</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U53"/>
+  <autoFilter ref="A1:U55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6049,11 +6317,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -6100,7 +6368,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>215C_G0008</t>
+          <t>G01512</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6128,7 +6396,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>215C_G0012</t>
+          <t>G01545</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6156,7 +6424,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>215C_G0014</t>
+          <t>G01547</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6184,7 +6452,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>215C_G0013</t>
+          <t>G01546</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6212,7 +6480,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>215C_G0019</t>
+          <t>G01580</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6240,7 +6508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>215C_G0012</t>
+          <t>G01545</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6268,7 +6536,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>216B_G0014</t>
+          <t>G01311</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6296,7 +6564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>216B_G0021</t>
+          <t>G01344</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6324,7 +6592,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>216B_G0024</t>
+          <t>G01347</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6352,7 +6620,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>216B_G0014</t>
+          <t>G01311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6380,7 +6648,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>216B_G0006</t>
+          <t>G01246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6408,7 +6676,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>216B_G0008</t>
+          <t>G01278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6436,7 +6704,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>217A_G0018</t>
+          <t>G01438</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6464,7 +6732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>217A_G0021</t>
+          <t>G01441</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6492,7 +6760,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>217A_G0007</t>
+          <t>G01375</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6520,7 +6788,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>217A_G0006</t>
+          <t>G01374</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6548,7 +6816,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>217A_G0012</t>
+          <t>G01406</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6576,7 +6844,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>217A_G0013</t>
+          <t>G01407</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6604,7 +6872,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>217A_G0008</t>
+          <t>G01376</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6632,7 +6900,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>217A_G0012</t>
+          <t>G01406</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6660,7 +6928,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>218B_G0024</t>
+          <t>G01336</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6688,7 +6956,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>218B_G0007</t>
+          <t>G01237</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6716,7 +6984,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>218B_G0009</t>
+          <t>G01239</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6744,7 +7012,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>218B_G0007</t>
+          <t>G01237</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6772,7 +7040,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>218B_G0015</t>
+          <t>G01272</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6800,7 +7068,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>218B_G0003</t>
+          <t>G01270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6828,7 +7096,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>218C_G0041</t>
+          <t>218C_D00191</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6845,7 +7113,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -6856,7 +7124,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>218C_G0060</t>
+          <t>218C_D00267</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6873,7 +7141,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -6884,7 +7152,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>219_G0020</t>
+          <t>G01204</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6912,7 +7180,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>219_G0002</t>
+          <t>G01137</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6940,7 +7208,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>219_G0025</t>
+          <t>G01209</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6968,7 +7236,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>219_G0020</t>
+          <t>G01139</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6996,7 +7264,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>220A_G0009</t>
+          <t>G01076</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7024,7 +7292,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>220A_G0013</t>
+          <t>G01140</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7052,7 +7320,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>220A_G0016</t>
+          <t>G01109</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7061,7 +7329,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -7080,7 +7348,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>220B_G0002</t>
+          <t>G01038</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7108,7 +7376,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>220B_G0007</t>
+          <t>G01072</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7136,7 +7404,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>220B_G0002</t>
+          <t>G01038</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7164,7 +7432,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>220B_G0012</t>
+          <t>G01106</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7192,7 +7460,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>220B_G0001</t>
+          <t>G01038</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7220,7 +7488,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>220B_G0002</t>
+          <t>G01040</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7248,7 +7516,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>220B_G0012</t>
+          <t>G01106</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7257,7 +7525,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7276,7 +7544,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>220B_G0004</t>
+          <t>G01040</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7304,7 +7572,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>221A_G0017</t>
+          <t>G01035</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7332,7 +7600,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>221A_G0030</t>
+          <t>G01097</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7360,12 +7628,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>221A_G0017</t>
+          <t>G01037</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -7388,12 +7656,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>221A_G0018</t>
+          <t>G01068</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -7411,25 +7679,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>222A_G0016</t>
+          <t>G01035</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -7439,17 +7707,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>222A_G0008</t>
+          <t>G01036</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -7457,7 +7725,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -7472,16 +7740,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>222A_G0009</t>
+          <t>G01510</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -7500,12 +7768,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>222A_G0020</t>
+          <t>G01475</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -7528,16 +7796,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>222A_G0013</t>
+          <t>G01476</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7556,12 +7824,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>222A_G0003</t>
+          <t>G01542</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -7579,21 +7847,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>223B_G0013</t>
+          <t>G01507</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7607,17 +7875,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>223B_G0007</t>
+          <t>G01442</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -7640,12 +7908,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>223B_G0017</t>
+          <t>G01197</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7668,16 +7936,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>223B_G0041</t>
+          <t>G01163</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -7696,12 +7964,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>223B_G0013</t>
+          <t>G01228</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -7716,8 +7984,64 @@
         <v>400</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>G01329</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>G01197</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F59"/>
+  <autoFilter ref="A1:F61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pauta_focalizada_pcsp.xlsx
+++ b/pauta_focalizada_pcsp.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_metodologia'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_ranking_cuadrantes'!$A$1:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_puntos_focalizados'!$A$1:$U$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_puntos_focalizados'!$A$1:$U$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_celdas_criticas'!$A$1:$F$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_eventos_pcsp'!$A$1:$F$179</definedName>
   </definedNames>
@@ -580,7 +580,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-12 13:04:39</t>
+          <t>2026-05-12 18:14:41</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1493,7 +1493,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Los Pajaritos &amp; Maipu</t>
+          <t>Av. Los Pajaritos &amp; Maipú</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1662,22 +1662,22 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-33.5069714</v>
+        <v>-33.5069746</v>
       </c>
       <c r="O2" t="n">
-        <v>-70.75733030000001</v>
+        <v>-70.7572827</v>
       </c>
       <c r="P2" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Los Pajaritos &amp; Maipu</t>
+          <t>Av. Los Pajaritos &amp; Maipú</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5069714,-70.7573303&amp;travelmode=walking</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5069746,-70.7572827&amp;travelmode=walking</t>
         </is>
       </c>
     </row>
@@ -1749,17 +1749,17 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>-33.5090537</v>
+        <v>-33.5090479</v>
       </c>
       <c r="O3" t="n">
-        <v>-70.758838</v>
+        <v>-70.7588612</v>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>46.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5090537,-70.7588380&amp;travelmode=walking</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5090479,-70.7588612&amp;travelmode=walking</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Iniciacion &amp; Los Capuchinos</t>
+          <t>Los Capuchinos &amp; Pje. Iniciación</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1836,22 +1836,22 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-33.4730838</v>
+        <v>-33.4730746</v>
       </c>
       <c r="O4" t="n">
-        <v>-70.73251740000001</v>
+        <v>-70.7325385</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Iniciacion &amp; Los Capuchinos</t>
+          <t>Los Capuchinos &amp; Pje. Iniciación</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4730838,-70.7325174&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4730746,-70.7325385&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dublin &amp; Las Parcelas</t>
+          <t>Av. Las Parcelas &amp; Pje. Reino Unido</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1923,22 +1923,22 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-33.4758398</v>
+        <v>-33.4759846</v>
       </c>
       <c r="O5" t="n">
-        <v>-70.7337339</v>
+        <v>-70.7337589</v>
       </c>
       <c r="P5" t="n">
-        <v>15.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Dublin &amp; Las Parcelas</t>
+          <t>Av. Las Parcelas &amp; Pje. Reino Unido</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4758398,-70.7337339&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4759846,-70.7337589&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Duraznal &amp; Las Torres</t>
+          <t>Dr. Livingstone &amp; Pje. Dakar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2010,27 +2010,27 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-33.4781355</v>
+        <v>-33.4780447</v>
       </c>
       <c r="O6" t="n">
-        <v>-70.7315126</v>
+        <v>-70.7360922</v>
       </c>
       <c r="P6" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>El Duraznal &amp; Las Torres</t>
+          <t>Dr. Livingstone &amp; Pje. Dakar</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>G01545</t>
+          <t>G01512</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4781355,-70.7315126&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4780447,-70.7360922&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doctor Livingstone &amp; Nigeria</t>
+          <t>Av. Simón Bolívar &amp; Dr. Livingstone</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2097,22 +2097,22 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-33.4800894</v>
+        <v>-33.4805035</v>
       </c>
       <c r="O7" t="n">
-        <v>-70.734459</v>
+        <v>-70.73397</v>
       </c>
       <c r="P7" t="n">
-        <v>66.90000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Doctor Livingstone &amp; Nigeria</t>
+          <t>Av. Simón Bolívar &amp; Dr. Livingstone</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4800894,-70.7344590&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4805035,-70.7339700&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dakar &amp; Doctor Livingstone</t>
+          <t>Av. Las Torres &amp; Pje. El Duraznal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2184,27 +2184,27 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-33.4780465</v>
+        <v>-33.4781411</v>
       </c>
       <c r="O8" t="n">
-        <v>-70.7360923</v>
+        <v>-70.73151609999999</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>19.7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Dakar &amp; Doctor Livingstone</t>
+          <t>Av. Las Torres &amp; Pje. El Duraznal</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>G01512</t>
+          <t>G01545</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4780465,-70.7360923&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4781411,-70.7315161&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amado Nervo &amp; Bramante</t>
+          <t>Pje. Ionesco &amp; Pje. Roberto Kock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2271,22 +2271,22 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-33.474024</v>
+        <v>-33.4740578</v>
       </c>
       <c r="O9" t="n">
-        <v>-70.7285696</v>
+        <v>-70.72904</v>
       </c>
       <c r="P9" t="n">
-        <v>35.8</v>
+        <v>19.3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Amado Nervo &amp; Bramante</t>
+          <t>Pje. Ionesco &amp; Pje. Roberto Kock</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4740240,-70.7285696&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4740578,-70.7290400&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Teatro Opera &amp; Teatro Recoleta</t>
+          <t>Pje. Teatro Ópera &amp; Teatro Recoleta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2358,22 +2358,22 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-33.4907514</v>
+        <v>-33.4906753</v>
       </c>
       <c r="O10" t="n">
-        <v>-70.7651177</v>
+        <v>-70.76509849999999</v>
       </c>
       <c r="P10" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Teatro Opera &amp; Teatro Recoleta</t>
+          <t>Pje. Teatro Ópera &amp; Teatro Recoleta</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4907514,-70.7651177&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4906753,-70.7650985&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Claudio Arrau &amp; Clavicordio</t>
+          <t>Claudio Arrau &amp; Pje. Teatro Caupolicán</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2445,22 +2445,22 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>-33.4906129</v>
+        <v>-33.4903933</v>
       </c>
       <c r="O11" t="n">
-        <v>-70.763896</v>
+        <v>-70.76387769999999</v>
       </c>
       <c r="P11" t="n">
-        <v>25.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Claudio Arrau &amp; Clavicordio</t>
+          <t>Claudio Arrau &amp; Pje. Teatro Caupolicán</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4906129,-70.7638960&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4903933,-70.7638777&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10 De Julio &amp; Campo De Batalla</t>
+          <t>Campo De Batalla &amp; Pje. Diez De Julio Huamachuco</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2532,22 +2532,22 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-33.4896701</v>
+        <v>-33.4896649</v>
       </c>
       <c r="O12" t="n">
-        <v>-70.7688747</v>
+        <v>-70.7689034</v>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
+        <v>50.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10 De Julio &amp; Campo De Batalla</t>
+          <t>Campo De Batalla &amp; Pje. Diez De Julio Huamachuco</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4896701,-70.7688747&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4896649,-70.7689034&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Batalla De Rancagua &amp; Campo De Batalla</t>
+          <t>Av. El Rosal &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2619,22 +2619,22 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-33.4878412</v>
+        <v>-33.4874823</v>
       </c>
       <c r="O13" t="n">
-        <v>-70.7704572</v>
+        <v>-70.7707388</v>
       </c>
       <c r="P13" t="n">
-        <v>30.3</v>
+        <v>22</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Batalla De Rancagua &amp; Campo De Batalla</t>
+          <t>Av. El Rosal &amp; Campo De Batalla</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4878412,-70.7704572&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4874823,-70.7707388&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2677,17 +2677,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La Sinfonia &amp; Volcan Maipo</t>
+          <t>Av. El Rosal &amp; Las Araucarias</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -2697,36 +2697,36 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-33.4897414</v>
+        <v>-33.480448</v>
       </c>
       <c r="O14" t="n">
-        <v>-70.7575111</v>
+        <v>-70.76025180000001</v>
       </c>
       <c r="P14" t="n">
-        <v>16.3</v>
+        <v>18.4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>La Sinfonia &amp; Volcan Maipo</t>
+          <t>Av. El Rosal &amp; Las Araucarias</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>G01344</t>
+          <t>G01347</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4897414,-70.7575111&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4804480,-70.7602518&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Rosal &amp; Las Araucarias</t>
+          <t>Av. La Sinfonía &amp; La Sinfonía</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2784,36 +2784,36 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>-33.4803684</v>
+        <v>-33.4896914</v>
       </c>
       <c r="O15" t="n">
-        <v>-70.7601743</v>
+        <v>-70.75754689999999</v>
       </c>
       <c r="P15" t="n">
-        <v>26.8</v>
+        <v>9.9</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>El Rosal &amp; Las Araucarias</t>
+          <t>Av. La Sinfonía &amp; La Sinfonía</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>G01347</t>
+          <t>G01344</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4803684,-70.7601743&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4896914,-70.7575469&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Libertador Bernardo O'higgins &amp; Paso De Los Patos</t>
+          <t>Aurora De Chile &amp; Padre De La Patria</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2861,14 +2861,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Robos violentos + Violencia intrafamiliar</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2880,27 +2880,27 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-33.5035963</v>
+        <v>-33.5037557</v>
       </c>
       <c r="O16" t="n">
-        <v>-70.7907591</v>
+        <v>-70.7891803</v>
       </c>
       <c r="P16" t="n">
-        <v>45.3</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Calera &amp; Cuatro Poniente | Libertador Bernardo O'higgins &amp; Paso De Los Patos</t>
+          <t>Aurora De Chile &amp; Padre De La Patria</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>G01076 | G01109</t>
+          <t>G01109</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5035963,-70.7907591&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5037557,-70.7891803&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -2938,56 +2938,56 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dawson &amp; Futaleufu</t>
+          <t>Libertador Bernardo O'Higgins Sur &amp; Mujeres Chilenas</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-33.5113905</v>
+        <v>-33.5037759</v>
       </c>
       <c r="O17" t="n">
-        <v>-70.78606430000001</v>
+        <v>-70.79165810000001</v>
       </c>
       <c r="P17" t="n">
-        <v>53.8</v>
+        <v>13.5</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Dawson &amp; Futaleufu</t>
+          <t>Libertador Bernardo O'Higgins Sur &amp; Mujeres Chilenas</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>G01140</t>
+          <t>G01076</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5113905,-70.7860643&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5037759,-70.7916581&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_220B_017</t>
+          <t>PF_PCSP_20260406_20260503_220A_017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>220B</t>
+          <t>220A</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Huaso &amp; Euridice</t>
+          <t>La Candelaria &amp; Pje. Dawson</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3054,27 +3054,27 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-33.5145065</v>
+        <v>-33.5114013</v>
       </c>
       <c r="O18" t="n">
-        <v>-70.7890127</v>
+        <v>-70.78593600000001</v>
       </c>
       <c r="P18" t="n">
-        <v>77.8</v>
+        <v>41.8</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>El Huaso &amp; Euridice</t>
+          <t>La Candelaria &amp; Pje. Dawson</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>G01106</t>
+          <t>G01140</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5145065,-70.7890127&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5114013,-70.7859360&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3108,25 +3108,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alceo &amp; Esquilo</t>
+          <t>Learcio &amp; Quinta Vergara</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3135,33 +3135,33 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-33.5185121</v>
+        <v>-33.5151934</v>
       </c>
       <c r="O19" t="n">
-        <v>-70.79471940000001</v>
+        <v>-70.7891576</v>
       </c>
       <c r="P19" t="n">
-        <v>41.7</v>
+        <v>49.4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Alceo &amp; Esquilo</t>
+          <t>Learcio &amp; Quinta Vergara</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>G01072</t>
+          <t>G01106</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185121,-70.7947194&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5151934,-70.7891576&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3195,28 +3195,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Campanario &amp; El Conquistador</t>
+          <t>La Galaxia &amp; Pje. Esquilo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -3225,30 +3225,30 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>-33.5205503</v>
+        <v>-33.5182025</v>
       </c>
       <c r="O20" t="n">
-        <v>-70.79690189999999</v>
+        <v>-70.79449390000001</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Campanario &amp; El Conquistador</t>
+          <t>La Galaxia &amp; Pje. Esquilo</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>G01038</t>
+          <t>G01072</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5205503,-70.7969019&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5182025,-70.7944939&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3282,60 +3282,60 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; El Potrero</t>
+          <t>El Conquistador &amp; Las Tinajas</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado + Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-33.522027</v>
+        <v>-33.5163542</v>
       </c>
       <c r="O21" t="n">
-        <v>-70.7969271</v>
+        <v>-70.7969315</v>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>61.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; El Potrero</t>
+          <t>El Conquistador &amp; Las Tinajas</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>G01038</t>
+          <t>G01040</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5220270,-70.7969271&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5163542,-70.7969315&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3369,55 +3369,55 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; Las Tinajas</t>
+          <t>El Conquistador &amp; Pje. Andrómeda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-33.5163693</v>
+        <v>-33.5146366</v>
       </c>
       <c r="O22" t="n">
-        <v>-70.7968735</v>
+        <v>-70.7969878</v>
       </c>
       <c r="P22" t="n">
-        <v>66.7</v>
+        <v>22.1</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>El Conquistador &amp; Las Tinajas</t>
+          <t>El Conquistador &amp; Pje. Andrómeda</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5163693,-70.7968735&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5146366,-70.7969878&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3456,11 +3456,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Andromeda &amp; El Conquistador</t>
+          <t>Campanario &amp; El Conquistador</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3489,27 +3489,27 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-33.5146254</v>
+        <v>-33.5205441</v>
       </c>
       <c r="O23" t="n">
-        <v>-70.79698380000001</v>
+        <v>-70.79684349999999</v>
       </c>
       <c r="P23" t="n">
-        <v>21.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Andromeda &amp; El Conquistador</t>
+          <t>Campanario &amp; El Conquistador</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>G01040</t>
+          <t>G01038</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5146254,-70.7969838&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5205441,-70.7968435&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_221A_023</t>
+          <t>PF_PCSP_20260406_20260503_220B_023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3539,15 +3539,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>221A</t>
+          <t>220B</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bosquealto &amp; Catemu</t>
+          <t>Av. Sur &amp; El Conquistador</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robo en lugar habitado + Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -3567,36 +3567,36 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>-33.53279</v>
+        <v>-33.5223257</v>
       </c>
       <c r="O24" t="n">
-        <v>-70.79795129999999</v>
+        <v>-70.7968293</v>
       </c>
       <c r="P24" t="n">
-        <v>57</v>
+        <v>13.8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Bosquealto &amp; Catemu</t>
+          <t>Av. Sur &amp; El Conquistador | El Conquistador &amp; El Potrero</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>G01035</t>
+          <t>G01038</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5327900,-70.7979513&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5223257,-70.7968293&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3630,55 +3630,55 @@
         </is>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Coltauco &amp; Llay-Llay</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Cam Del Leñador &amp; Litueche</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-33.5340813</v>
+        <v>-33.533378</v>
       </c>
       <c r="O25" t="n">
-        <v>-70.79976929999999</v>
+        <v>-70.797608</v>
       </c>
       <c r="P25" t="n">
-        <v>48.5</v>
+        <v>18.2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Cam Del Leñador &amp; Litueche</t>
+          <t>Coltauco &amp; Llay-Llay</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5340813,-70.7997693&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5333780,-70.7976080&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3717,60 +3717,60 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alfredo Silva Carvallo &amp; Cuatro Poniente</t>
+          <t>Litueche &amp; Pje. Pichidegua</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-33.5319846</v>
+        <v>-33.5338639</v>
       </c>
       <c r="O26" t="n">
-        <v>-70.79345929999999</v>
+        <v>-70.7996772</v>
       </c>
       <c r="P26" t="n">
-        <v>21.1</v>
+        <v>31.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Alfredo Silva Carvallo &amp; Cuatro Poniente</t>
+          <t>Litueche &amp; Pje. Pichidegua</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>G01068</t>
+          <t>G01035</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5319846,-70.7934593&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5338639,-70.7996772&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3804,11 +3804,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
+          <t>El Conquistador &amp; Pje. Ester</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3837,22 +3837,22 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-33.5286591</v>
+        <v>-33.5290509</v>
       </c>
       <c r="O27" t="n">
-        <v>-70.7973439</v>
+        <v>-70.7974208</v>
       </c>
       <c r="P27" t="n">
-        <v>42.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Concejala Sra. Hilda Porras &amp; El Conquistador</t>
+          <t>El Conquistador &amp; Pje. Ester</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5286591,-70.7973439&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5290509,-70.7974208&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3891,11 +3891,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Faro De Alejandria &amp; Rosita Renard</t>
+          <t>Av. 4 Poniente &amp; Av. Alfredo Silva Carvallo</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3924,27 +3924,27 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-33.5256375</v>
+        <v>-33.5321158</v>
       </c>
       <c r="O28" t="n">
-        <v>-70.7983357</v>
+        <v>-70.7933137</v>
       </c>
       <c r="P28" t="n">
-        <v>180.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Faro De Alejandria &amp; Rosita Renard</t>
+          <t>Av. 4 Poniente &amp; Av. Alfredo Silva Carvallo</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>G01037</t>
+          <t>G01068</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5256375,-70.7983357&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5321158,-70.7933137&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -3978,31 +3978,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Sauco &amp; Portal Del Bosque</t>
+          <t>Pje. Los Astronomos &amp; Valle De Los Reyes</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4011,27 +4011,27 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-33.5458374</v>
+        <v>-33.524149</v>
       </c>
       <c r="O29" t="n">
-        <v>-70.7901864</v>
+        <v>-70.79846809999999</v>
       </c>
       <c r="P29" t="n">
-        <v>78.5</v>
+        <v>15.4</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>El Sauco &amp; Portal Del Bosque</t>
+          <t>Pje. Los Astronomos &amp; Valle De Los Reyes</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>G01097</t>
+          <t>G01037</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5458374,-70.7901864&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5241490,-70.7984681&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4051,25 +4051,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_217A_029</t>
+          <t>PF_PCSP_20260406_20260503_221A_029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Móviles</t>
+          <t>Motoristas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>217A</t>
+          <t>221A</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anunciacion &amp; Judith</t>
+          <t>El Avellano &amp; El Ulmo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4098,27 +4098,27 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-33.4955146</v>
+        <v>-33.54666</v>
       </c>
       <c r="O30" t="n">
-        <v>-70.7550313</v>
+        <v>-70.7906627</v>
       </c>
       <c r="P30" t="n">
-        <v>27.4</v>
+        <v>23.8</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Anunciacion &amp; Judith</t>
+          <t>El Avellano &amp; El Ulmo</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>G01375</t>
+          <t>G01097</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4955146,-70.7550313&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5466600,-70.7906627&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4152,60 +4152,60 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Anunciación &amp; Judith</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Cecilia &amp; Meli</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Violencia intrafamiliar</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-33.4950829</v>
+        <v>-33.4955137</v>
       </c>
       <c r="O31" t="n">
-        <v>-70.75292399999999</v>
+        <v>-70.7550517</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>29.2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Cecilia &amp; Meli</t>
+          <t>Anunciación &amp; Judith</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>G01376</t>
+          <t>G01375</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4950829,-70.7529240&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4955137,-70.7550517&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4239,60 +4239,60 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Central Gonzalo Perez Llona &amp; Primera Transversal</t>
+          <t>Anunciación &amp; Cecilia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-33.5002405</v>
+        <v>-33.495052</v>
       </c>
       <c r="O32" t="n">
-        <v>-70.75199139999999</v>
+        <v>-70.75295989999999</v>
       </c>
       <c r="P32" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Central Gonzalo Perez Llona &amp; Primera Transversal</t>
+          <t>Anunciación &amp; Cecilia</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>G01407</t>
+          <t>G01376</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5002405,-70.7519914&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4950520,-70.7529599&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4326,11 +4326,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Covadonga &amp; El Sol</t>
+          <t>Av. Central Gonzalo Pérez Llona &amp; Primera Transversal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4359,27 +4359,27 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-33.5034736</v>
+        <v>-33.5002353</v>
       </c>
       <c r="O33" t="n">
-        <v>-70.7498313</v>
+        <v>-70.7520075</v>
       </c>
       <c r="P33" t="n">
-        <v>30.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Covadonga &amp; El Sol</t>
+          <t>Av. Central Gonzalo Pérez Llona &amp; Primera Transversal</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>G01406</t>
+          <t>G01407</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5034736,-70.7498313&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5002353,-70.7520075&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4413,55 +4413,55 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Presidente Kennedy &amp; Uno Sur</t>
+          <t>Pdte. Kennedy &amp; Pje. Grumete Bustos</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-33.506299</v>
+        <v>-33.5033943</v>
       </c>
       <c r="O34" t="n">
-        <v>-70.74939689999999</v>
+        <v>-70.7490396</v>
       </c>
       <c r="P34" t="n">
-        <v>16.8</v>
+        <v>55</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Presidente Kennedy &amp; Uno Sur</t>
+          <t>Pdte. Kennedy &amp; Pje. Grumete Bustos</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5062990,-70.7493969&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5033943,-70.7490396&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5 De Abril &amp; Segunda Transversal</t>
+          <t>1 Sur &amp; Pdte. Kennedy</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -4527,33 +4527,33 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>-33.5103631</v>
+        <v>-33.5062953</v>
       </c>
       <c r="O35" t="n">
-        <v>-70.74719260000001</v>
+        <v>-70.7494028</v>
       </c>
       <c r="P35" t="n">
-        <v>80.40000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>5 De Abril &amp; Segunda Transversal</t>
+          <t>1 Sur &amp; Pdte. Kennedy</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>G01438</t>
+          <t>G01406</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5103631,-70.7471926&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5062953,-70.7494028&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_218B_035</t>
+          <t>PF_PCSP_20260406_20260503_217A_035</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4583,64 +4583,64 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>218B</t>
+          <t>217A</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Campanario &amp; El Principe</t>
+          <t>Av. 5 De Abril &amp; Av. Segunda Transversal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado + Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>-33.519661</v>
+        <v>-33.5102549</v>
       </c>
       <c r="O36" t="n">
-        <v>-70.7714407</v>
+        <v>-70.74723090000001</v>
       </c>
       <c r="P36" t="n">
-        <v>19.2</v>
+        <v>74.5</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Campanario &amp; Del Rey | Campanario &amp; El Principe</t>
+          <t>Av. 5 De Abril &amp; Av. Segunda Transversal</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>G01237 | G01270</t>
+          <t>G01438</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5196610,-70.7714407&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5102549,-70.7472309&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4674,31 +4674,31 @@
         </is>
       </c>
       <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Campanario &amp; Pje. El Príncipe</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Del Rey &amp; Los Escritores</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-33.5185017</v>
+        <v>-33.5196596</v>
       </c>
       <c r="O37" t="n">
-        <v>-70.770884</v>
+        <v>-70.771463</v>
       </c>
       <c r="P37" t="n">
-        <v>10.7</v>
+        <v>18.3</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Del Rey &amp; Los Escritores</t>
+          <t>Campanario &amp; Pje. El Príncipe</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185017,-70.7708840&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5196596,-70.7714630&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4761,11 +4761,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Del Pontifice &amp; Republica</t>
+          <t>Pje. Los Aviadores &amp; Pje. Los Poetas</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4788,33 +4788,33 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-33.5129099</v>
+        <v>-33.5200961</v>
       </c>
       <c r="O38" t="n">
-        <v>-70.7670775</v>
+        <v>-70.7701047</v>
       </c>
       <c r="P38" t="n">
-        <v>81.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Del Pontifice &amp; Republica</t>
+          <t>Pje. Los Aviadores &amp; Pje. Los Poetas</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>G01272</t>
+          <t>G01270</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5129099,-70.7670775&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5200961,-70.7701047&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4848,31 +4848,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alemania &amp; Jose Manuel Borgoño</t>
+          <t>Del Rey &amp; Pje. Los Escritores</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4881,27 +4881,27 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-33.5117929</v>
+        <v>-33.5184413</v>
       </c>
       <c r="O39" t="n">
-        <v>-70.77179270000001</v>
+        <v>-70.7709098</v>
       </c>
       <c r="P39" t="n">
-        <v>18.2</v>
+        <v>6.6</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Alemania &amp; Jose Manuel Borgoño</t>
+          <t>Del Rey &amp; Pje. Los Escritores</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>G01239</t>
+          <t>G01237</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5117929,-70.7717927&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5184413,-70.7709098&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -4935,25 +4935,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
+          <t>Del Pontífice &amp; República</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Alcohol y drogas en vía pública</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4962,33 +4962,33 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>-33.520565</v>
+        <v>-33.5129148</v>
       </c>
       <c r="O40" t="n">
-        <v>-70.7590924</v>
+        <v>-70.7671014</v>
       </c>
       <c r="P40" t="n">
-        <v>15.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Los Pascuenses &amp; Los Pascuenses Poniente</t>
+          <t>Del Pontífice &amp; República</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>G01336</t>
+          <t>G01272</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5205650,-70.7590924&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5129148,-70.7671014&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_219_040</t>
+          <t>PF_PCSP_20260406_20260503_218B_040</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5018,64 +5018,64 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218B</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amaltea &amp; El Olimpo</t>
+          <t>José Manuel Borgoño &amp; Pje. Alemania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-33.5024761</v>
+        <v>-33.5117999</v>
       </c>
       <c r="O41" t="n">
-        <v>-70.7755947</v>
+        <v>-70.77179769999999</v>
       </c>
       <c r="P41" t="n">
-        <v>33.9</v>
+        <v>18.4</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Amaltea &amp; El Olimpo</t>
+          <t>José Manuel Borgoño &amp; Pje. Alemania</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>G01209</t>
+          <t>G01239</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5024761,-70.7755947&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5117999,-70.7717977&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_219_041</t>
+          <t>PF_PCSP_20260406_20260503_218B_041</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5105,29 +5105,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218B</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chinquihue &amp; El Cequion</t>
+          <t>Av. Sur &amp; Pje. Los Pascuenses</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Alcohol y drogas en vía pública</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5136,33 +5136,33 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>-33.5141403</v>
+        <v>-33.520931</v>
       </c>
       <c r="O42" t="n">
-        <v>-70.7851647</v>
+        <v>-70.7591065</v>
       </c>
       <c r="P42" t="n">
-        <v>68</v>
+        <v>28.2</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Chinquihue &amp; El Cequion</t>
+          <t>Av. Sur &amp; Pje. Los Pascuenses</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>G01139</t>
+          <t>G01336</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5141403,-70.7851647&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5209310,-70.7591065&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5196,60 +5196,60 @@
         </is>
       </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Av. El Olimpo &amp; Pje. Amaltea</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
         <v>3</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Disprosio &amp; Las Olimpiadas</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-33.5218854</v>
+        <v>-33.5022617</v>
       </c>
       <c r="O43" t="n">
-        <v>-70.78387189999999</v>
+        <v>-70.7755951</v>
       </c>
       <c r="P43" t="n">
-        <v>31.4</v>
+        <v>15.9</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Disprosio &amp; Las Olimpiadas</t>
+          <t>Av. El Olimpo &amp; Pje. Amaltea</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>G01137</t>
+          <t>G01209</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5218854,-70.7838719&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5022617,-70.7755951&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5283,60 +5283,60 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Filidor &amp; Los Coros</t>
+          <t>Av. Las Naciones &amp; Pje. Los Zarzales</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I44" t="n">
         <v>2</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-33.5185804</v>
+        <v>-33.5135989</v>
       </c>
       <c r="O44" t="n">
-        <v>-70.7759921</v>
+        <v>-70.78503739999999</v>
       </c>
       <c r="P44" t="n">
-        <v>43.7</v>
+        <v>37.3</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Filidor &amp; Los Coros</t>
+          <t>Av. Las Naciones &amp; Pje. Los Zarzales</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>G01204</t>
+          <t>G01139</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5185804,-70.7759921&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5135989,-70.7850374&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_222A_044</t>
+          <t>PF_PCSP_20260406_20260503_219_044</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5366,35 +5366,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
+          <t>Av. Sur &amp; Universidad Católica</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5403,27 +5403,27 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-33.4874962</v>
+        <v>-33.5218989</v>
       </c>
       <c r="O45" t="n">
-        <v>-70.737493</v>
+        <v>-70.78422089999999</v>
       </c>
       <c r="P45" t="n">
-        <v>47.3</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
+          <t>Av. Sur &amp; Universidad Católica</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>G01510</t>
+          <t>G01137</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4874962,-70.7374930&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5218989,-70.7842209&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_222A_045</t>
+          <t>PF_PCSP_20260406_20260503_219_045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5453,32 +5453,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>222A</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pje. Filidor &amp; Pje. Los Coros</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>2</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Hernando Bravo &amp; Juan Bohon</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -5490,27 +5490,27 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-33.4891265</v>
+        <v>-33.5185751</v>
       </c>
       <c r="O46" t="n">
-        <v>-70.7348198</v>
+        <v>-70.77600200000001</v>
       </c>
       <c r="P46" t="n">
-        <v>53.2</v>
+        <v>44.5</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Hernando Bravo &amp; Juan Bohon</t>
+          <t>Pje. Filidor &amp; Pje. Los Coros</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>G01542</t>
+          <t>G01204</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4891265,-70.7348198&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5185751,-70.7760020&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5544,31 +5544,31 @@
         </is>
       </c>
       <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Robo en lugar habitado</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
         <v>3</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Carmela Larrain &amp; Dolores Bernales</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Robos violentos</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5577,27 +5577,27 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-33.4898862</v>
+        <v>-33.4874928</v>
       </c>
       <c r="O47" t="n">
-        <v>-70.7398524</v>
+        <v>-70.7375096</v>
       </c>
       <c r="P47" t="n">
-        <v>74.90000000000001</v>
+        <v>47</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Carmela Larrain &amp; Dolores Bernales</t>
+          <t>Las Golondrinas Oriente &amp; Los Ministros</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>G01476</t>
+          <t>G01510</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4898862,-70.7398524&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4874928,-70.7375096&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5631,31 +5631,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>El Pesebre &amp; La Adoracion</t>
+          <t>Av. Lumen &amp; Los Presidentes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5664,27 +5664,27 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-33.4939805</v>
+        <v>-33.4886191</v>
       </c>
       <c r="O48" t="n">
-        <v>-70.7400719</v>
+        <v>-70.73472630000001</v>
       </c>
       <c r="P48" t="n">
-        <v>49.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>El Pesebre &amp; La Adoracion</t>
+          <t>Av. Lumen &amp; Los Presidentes</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>G01475</t>
+          <t>G01542</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4939805,-70.7400719&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4886191,-70.7347263&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5718,60 +5718,60 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lumen &amp; Tres Norte</t>
+          <t>Alaska &amp; Pje. Carmela Larraín</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robos violentos</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-33.4959182</v>
+        <v>-33.4907023</v>
       </c>
       <c r="O49" t="n">
-        <v>-70.7365563</v>
+        <v>-70.7399102</v>
       </c>
       <c r="P49" t="n">
-        <v>84.8</v>
+        <v>18.8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Lumen &amp; Tres Norte</t>
+          <t>Alaska &amp; Pje. Carmela Larraín</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>G01507</t>
+          <t>G01476</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4959182,-70.7365563&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4907023,-70.7399102&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5805,21 +5805,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alonso De Ercilla &amp; Jose Santos Gonzalez</t>
+          <t>Las Golondrinas &amp; Sagrado Corazón</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -5829,36 +5829,36 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-33.4942642</v>
+        <v>-33.4942484</v>
       </c>
       <c r="O50" t="n">
-        <v>-70.7451442</v>
+        <v>-70.7396803</v>
       </c>
       <c r="P50" t="n">
-        <v>30.8</v>
+        <v>53.6</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Alonso De Ercilla &amp; Jose Santos Gonzalez</t>
+          <t>Las Golondrinas &amp; Sagrado Corazón</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>G01442</t>
+          <t>G01475</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.4942642,-70.7451442&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4942484,-70.7396803&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_223B_050</t>
+          <t>PF_PCSP_20260406_20260503_222A_050</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5888,15 +5888,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Empedrado &amp; Israel</t>
+          <t>3 Norte &amp; Pje. La Pinta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5925,27 +5925,27 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-33.5458136</v>
+        <v>-33.4961547</v>
       </c>
       <c r="O51" t="n">
-        <v>-70.76161089999999</v>
+        <v>-70.7358156</v>
       </c>
       <c r="P51" t="n">
-        <v>23.1</v>
+        <v>61.3</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Empedrado &amp; Israel</t>
+          <t>3 Norte &amp; Pje. La Pinta</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>G01329</t>
+          <t>G01507</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5458136,-70.7616109&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4961547,-70.7358156&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PF_PCSP_20260406_20260503_223B_051</t>
+          <t>PF_PCSP_20260406_20260503_222A_051</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5975,64 +5975,64 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>223B</t>
+          <t>222A</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caronte &amp; El Libano Poniente</t>
+          <t>Pje. Puerto Cárdenas &amp; Pje. Puerto Viejo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Robos violentos</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-33.54948</v>
+        <v>-33.4938208</v>
       </c>
       <c r="O52" t="n">
-        <v>-70.7728819</v>
+        <v>-70.74522399999999</v>
       </c>
       <c r="P52" t="n">
-        <v>23.4</v>
+        <v>36.9</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Caronte &amp; El Libano Poniente</t>
+          <t>Pje. Puerto Cárdenas &amp; Pje. Puerto Viejo</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>G01228</t>
+          <t>G01442</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5494800,-70.7728819&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.4938208,-70.7452240&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -6066,60 +6066,60 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Diputado Angel Fantuzzi Hernandez &amp; Madreselva</t>
+          <t>Los Beduinos &amp; Pje. Los Beduinos 5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Robo en lugar habitado</t>
+          <t>Violencia intrafamiliar</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-33.5450065</v>
+        <v>-33.5459002</v>
       </c>
       <c r="O53" t="n">
-        <v>-70.7793266</v>
+        <v>-70.7613449</v>
       </c>
       <c r="P53" t="n">
-        <v>3.7</v>
+        <v>15.7</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Diputado Angel Fantuzzi Hernandez &amp; Madreselva</t>
+          <t>Los Beduinos &amp; Pje. Los Beduinos 5</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>G01197</t>
+          <t>G01329</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5450065,-70.7793266&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5459002,-70.7613449&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Esdras &amp; Madreselva</t>
+          <t>Caronte &amp; Esdras</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6186,27 +6186,27 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-33.5461565</v>
+        <v>-33.5496366</v>
       </c>
       <c r="O54" t="n">
-        <v>-70.78067249999999</v>
+        <v>-70.77311570000001</v>
       </c>
       <c r="P54" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Esdras &amp; Madreselva</t>
+          <t>Caronte &amp; Esdras</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>G01163</t>
+          <t>G01228</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5461565,-70.7806725&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5496366,-70.7731157&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Heliopolis &amp; Sahara</t>
+          <t>Diputado Ángel Fantuzzi Hernández &amp; Madreselva</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Violencia intrafamiliar</t>
+          <t>Robo en lugar habitado</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -6264,31 +6264,31 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-33.542362</v>
+        <v>-33.5450083</v>
       </c>
       <c r="O55" t="n">
-        <v>-70.7769976</v>
+        <v>-70.7793231</v>
       </c>
       <c r="P55" t="n">
-        <v>24.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>mismo_cuadrante</t>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Heliopolis &amp; Sahara</t>
+          <t>Diputado Ángel Fantuzzi Hernández &amp; Madreselva</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6301,12 +6301,186 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/dir/?api=1&amp;destination=-33.5423620,-70.7769976&amp;travelmode=driving</t>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5450083,-70.7793231&amp;travelmode=driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503_223B_055</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Esdras &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Robos violentos</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-33.5461811</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-70.78062730000001</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Esdras &amp; Madreselva</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>G01163</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>400</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5461811,-70.7806273&amp;travelmode=driving</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PF_PCSP_20260406_20260503_223B_056</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Móviles</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>223B</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pje. Heliópolis &amp; Pje. Sahara</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-33.5423656</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-70.7770051</v>
+      </c>
+      <c r="P57" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>toda_comuna_sin_intersecciones_en_cuadrante</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Pje. Heliópolis &amp; Pje. Sahara</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>G01197</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>400</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/?api=1&amp;origin=Current%20Location&amp;destination=-33.5423656,-70.7770051&amp;travelmode=driving</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U55"/>
+  <autoFilter ref="A1:U57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pauta_focalizada_pcsp.xlsx
+++ b/pauta_focalizada_pcsp.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-27 17:15:37</t>
+          <t>2026-05-27 17:54:33</t>
         </is>
       </c>
     </row>

--- a/pauta_focalizada_pcsp.xlsx
+++ b/pauta_focalizada_pcsp.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-01 11:35:21</t>
+          <t>2026-06-01 15:45:29</t>
         </is>
       </c>
     </row>
